--- a/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8859060402684564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.8895705521472392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8838709677419355</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="F2" t="n">
-        <v>0.893899917287014</v>
+        <v>0.8858646525994285</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6453900709219859</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5787234042553192</v>
+        <v>0.584920634920635</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6821428571428572</v>
+        <v>0.5198198198198198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5488095238095239</v>
+        <v>0.6784172661870504</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6137664640324215</v>
+        <v>0.594003715946162</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6643356643356644</v>
+        <v>0.6008285609845254</v>
       </c>
       <c r="C4" t="n">
-        <v>0.59375</v>
+        <v>0.5995256916996048</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7061213434452871</v>
+        <v>0.5205882352941177</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5596590909090909</v>
+        <v>0.6955318307631475</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6309665246725106</v>
+        <v>0.6041185796853489</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8902635825712749</v>
+        <v>0.8591352597688654</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8713942307692307</v>
+        <v>0.8745417407220734</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9033656030475659</v>
+        <v>0.8637675929267412</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8643695014662756</v>
+        <v>0.8977060898769084</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8823482294635867</v>
+        <v>0.8737876708236471</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8676122931442081</v>
+        <v>0.8241071428571429</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8127659574468085</v>
+        <v>0.6158730158730158</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8152380952380952</v>
+        <v>0.6887387387387387</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7438095238095238</v>
+        <v>0.7745803357314149</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8098564674096589</v>
+        <v>0.7258248083000781</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[135   6]
- [ 10   5]]</t>
+          <t>[[131, 9], [12, 4]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[135   6]
- [ 12   3]]</t>
+          <t>[[129, 6], [11, 3]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[135   5]
- [  9   6]]</t>
+          <t>[[144, 4], [14, 1]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[135   5]
- [ 13   2]]</t>
+          <t>[[133, 6], [9, 6]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[135, 6], [11, 4]]</t>
+          <t>[[134, 6], [12, 4]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8525641025641025</v>
+        <v>0.7046979865771812</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8258064516129032</v>
+        <v>0.7607361963190185</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7677419354838709</v>
+        <v>0.7467532467532467</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8166563275434242</v>
+        <v>0.7357391651046693</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6921985815602837</v>
+        <v>0.65625</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7099290780141844</v>
+        <v>0.676984126984127</v>
       </c>
       <c r="D9" t="n">
-        <v>0.725</v>
+        <v>0.5986486486486486</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6928571428571428</v>
+        <v>0.681294964028777</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7049962006079027</v>
+        <v>0.6532944349153882</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6295793758480326</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.663003663003663</v>
+        <v>0.5519409513395298</v>
       </c>
       <c r="D10" t="n">
-        <v>0.649056603773585</v>
+        <v>0.5467379679144385</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5963541666666666</v>
+        <v>0.5802054938142168</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6344984523229869</v>
+        <v>0.561387769933713</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.844379501095919</v>
+        <v>0.7786324786324786</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8671456748379825</v>
+        <v>0.7643961382792519</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8499087035909922</v>
+        <v>0.8008608641448771</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8084677419354839</v>
+        <v>0.7931118996331828</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8424754053650945</v>
+        <v>0.7842503451724476</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7494089834515366</v>
+        <v>0.740625</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8330969267139481</v>
+        <v>0.653968253968254</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7742857142857142</v>
+        <v>0.618018018018018</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6866666666666665</v>
+        <v>0.7266187050359713</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7608645727794663</v>
+        <v>0.6848074942555608</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[120  21]
- [  7   8]]</t>
+          <t>[[105, 35], [7, 9]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[125  16]
- [  7   8]]</t>
+          <t>[[96, 39], [5, 9]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[119  21]
- [  6   9]]</t>
+          <t>[[118, 30], [9, 6]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[110  30]
- [  6   9]]</t>
+          <t>[[106, 33], [6, 9]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[118, 22], [6, 8]]</t>
+          <t>[[106, 34], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -762,16 +755,16 @@
         <v>0.8910256410256411</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.9060402684563759</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.852760736196319</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.9025974025974026</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8842638544251448</v>
+        <v>0.8881060120689346</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4929078014184397</v>
+        <v>0.4964285714285714</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4787234042553192</v>
+        <v>0.532010582010582</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5928571428571429</v>
+        <v>0.4695945945945946</v>
       </c>
       <c r="E15" t="n">
-        <v>0.511904761904762</v>
+        <v>0.5594724220623501</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5190982776089159</v>
+        <v>0.5143765425240245</v>
       </c>
     </row>
     <row r="16">
@@ -806,16 +799,16 @@
         <v>0.4711864406779661</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4639175257731959</v>
+        <v>0.537677304964539</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6258620689655172</v>
+        <v>0.4602649006622517</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5107323232323232</v>
+        <v>0.5793116008013113</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5179245896622506</v>
+        <v>0.5121100617765171</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8517601043024772</v>
+        <v>0.8457192524989134</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8386201427438541</v>
+        <v>0.8728045123518492</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8886540600667409</v>
+        <v>0.8358184699142729</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8492994460736396</v>
+        <v>0.8762555965251285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8570834382966779</v>
+        <v>0.857649457822541</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5938534278959811</v>
+        <v>0.5854910714285714</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5106382978723404</v>
+        <v>0.5904761904761905</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7114285714285714</v>
+        <v>0.4986486486486486</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5133333333333333</v>
+        <v>0.6520383693045565</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5823134076325565</v>
+        <v>0.5816635699644918</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 15   0]]</t>
+          <t>[[139, 1], [16, 0]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[135   6]
- [ 15   0]]</t>
+          <t>[[134, 1], [13, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 12   3]]</t>
+          <t>[[139, 9], [15, 0]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[134   6]
- [ 14   1]]</t>
+          <t>[[137, 2], [13, 2]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[136, 4], [14, 1]]</t>
+          <t>[[137, 3], [14, 1]]</t>
         </is>
       </c>
     </row>
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6282051282051282</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.6711409395973155</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6967741935483871</v>
+        <v>0.6073619631901841</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6064516129032258</v>
+        <v>0.6688311688311688</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6463192721257237</v>
+        <v>0.6535001845713337</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5858156028368795</v>
+        <v>0.6205357142857143</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5702127659574467</v>
+        <v>0.5944444444444444</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.5740990990990991</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5738095238095238</v>
+        <v>0.6083932853717027</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6032928064842958</v>
+        <v>0.5993681358002401</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4862593686123098</v>
+        <v>0.521133412042503</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4922854387656702</v>
+        <v>0.506855791962175</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5525459124132424</v>
+        <v>0.4699186991869919</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4729948163424559</v>
+        <v>0.5135938564439214</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5010213840334196</v>
+        <v>0.5028754399088978</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7043711455476162</v>
+        <v>0.7309720582447856</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7236110080854535</v>
+        <v>0.7380011740999889</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7574156299347548</v>
+        <v>0.6901591101800589</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6868678877539461</v>
+        <v>0.7348516350188488</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7180664178304427</v>
+        <v>0.7234959943859205</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6208037825059102</v>
+        <v>0.7258928571428571</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6619385342789599</v>
+        <v>0.7005291005291006</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7633333333333334</v>
+        <v>0.6256756756756757</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6661904761904762</v>
+        <v>0.6326139088729017</v>
       </c>
       <c r="F24" t="n">
-        <v>0.67806653157717</v>
+        <v>0.6711778855551338</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[90 51]
- [ 7  8]]</t>
+          <t>[[95, 45], [7, 9]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[95 46]
- [ 8  7]]</t>
+          <t>[[93, 42], [7, 7]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[98 42]
- [ 5 10]]</t>
+          <t>[[91, 57], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[86 54]
- [ 7  8]]</t>
+          <t>[[95, 44], [7, 8]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[92, 48], [7, 8]]</t>
+          <t>[[94, 47], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8910256410256411</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.8993288590604027</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8895705521472392</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8903225806451613</v>
+        <v>0.8896103896103896</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8970947063688999</v>
+        <v>0.8923838604609182</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4964539007092199</v>
+        <v>0.5241071428571429</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5297872340425532</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5261904761904762</v>
+        <v>0.4898648648648649</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4928571428571429</v>
+        <v>0.4928057553956834</v>
       </c>
       <c r="F27" t="n">
-        <v>0.511322188449848</v>
+        <v>0.5007685148534968</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.472972972972973</v>
+        <v>0.5236213400395187</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5333998005982054</v>
+        <v>0.4734982332155477</v>
       </c>
       <c r="D28" t="n">
-        <v>0.528158295281583</v>
+        <v>0.4707792207792208</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4709897610921502</v>
+        <v>0.4707903780068728</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5013802074862278</v>
+        <v>0.48467229301029</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8549896049896051</v>
+        <v>0.8561624591802425</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8692000920315974</v>
+        <v>0.858016932672469</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8644866696126086</v>
+        <v>0.8549119592064377</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8508202135858196</v>
+        <v>0.8498683447137055</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8598741450549077</v>
+        <v>0.8547399239432136</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8127659574468085</v>
+        <v>0.8191964285714286</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7877068557919622</v>
+        <v>0.7222222222222221</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.7556306306306306</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7166666666666667</v>
+        <v>0.73621103117506</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7807134414049308</v>
+        <v>0.7583150781498353</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 15   0]]</t>
+          <t>[[138, 2], [15, 1]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[140   1]
- [ 14   1]]</t>
+          <t>[[134, 1], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 14   1]]</t>
+          <t>[[145, 3], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 15   0]]</t>
+          <t>[[137, 2], [15, 0]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[139, 2], [14, 0]]</t>
+          <t>[[138, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8858646525994285</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01335245530990876</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.594003715946162</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05637533791366504</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6041185796853489</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06197906854300027</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8737876708236471</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01489760469167338</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7258248083000781</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.07984561972100748</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[134, 6], [12, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7357391651046693</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.02082316363912215</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6532944349153882</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.03293982567736568</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.561387769933713</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.01309420256750498</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7842503451724476</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01396590888389241</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6848074942555608</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05068447536484409</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[106, 34], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8881060120689346</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.02115094980949551</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5143765425240245</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03417656443656252</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5121100617765171</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04881699055226135</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.857649457822541</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01728283763825468</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5816635699644918</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.05462692008289217</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[137, 3], [14, 1]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6535001845713337</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02668486012350779</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5993681358002401</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01726475206958335</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5028754399088978</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01968646718515493</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7234959943859205</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.01940740961655164</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6711778855551338</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04304896438288432</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[94, 47], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Conch1_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8923838604609182</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.004052302117554702</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5007685148534968</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01366553527284544</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.48467229301029</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02251451141464848</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8547399239432136</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.003021765751732424</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7583150781498353</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03709793872075212</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[138, 2], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Caption_based_aggregation/Conch1_5/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="C8" t="n">
         <v>0.7046979865771812</v>
@@ -619,10 +619,10 @@
         <v>0.7607361963190185</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7467532467532467</v>
+        <v>0.7922077922077922</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7357391651046693</v>
+        <v>0.7438976732631775</v>
       </c>
     </row>
     <row r="9">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.65625</v>
+        <v>0.6767857142857143</v>
       </c>
       <c r="C9" t="n">
         <v>0.676984126984127</v>
@@ -641,10 +641,10 @@
         <v>0.5986486486486486</v>
       </c>
       <c r="E9" t="n">
-        <v>0.681294964028777</v>
+        <v>0.7362110311750599</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6532944349153882</v>
+        <v>0.6721573802733875</v>
       </c>
     </row>
     <row r="10">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5675403225806452</v>
       </c>
       <c r="C10" t="n">
         <v>0.5519409513395298</v>
@@ -663,10 +663,10 @@
         <v>0.5467379679144385</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5802054938142168</v>
+        <v>0.6298076923076923</v>
       </c>
       <c r="F10" t="n">
-        <v>0.561387769933713</v>
+        <v>0.5740067335355765</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7786324786324786</v>
+        <v>0.7702646815550042</v>
       </c>
       <c r="C11" t="n">
         <v>0.7643961382792519</v>
@@ -685,10 +685,10 @@
         <v>0.8008608641448771</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7931118996331828</v>
+        <v>0.8272352647352648</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7842503451724476</v>
+        <v>0.7906892371785995</v>
       </c>
     </row>
     <row r="12">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.740625</v>
+        <v>0.7263392857142856</v>
       </c>
       <c r="C12" t="n">
         <v>0.653968253968254</v>
@@ -707,10 +707,10 @@
         <v>0.618018018018018</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7266187050359713</v>
+        <v>0.7851318944844126</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6848074942555608</v>
+        <v>0.6958643630462426</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[105, 35], [7, 9]]</t>
+          <t>[[102, 38], [6, 10]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[106, 33], [6, 9]]</t>
+          <t>[[112, 27], [5, 10]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[106, 34], [7, 8]]</t>
+          <t>[[107, 34], [6, 9]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7357391651046693</v>
+        <v>0.7438976732631775</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02082316363912215</v>
+        <v>0.03473962855780487</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6532944349153882</v>
+        <v>0.6721573802733875</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03293982567736568</v>
+        <v>0.04886492294696294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.561387769933713</v>
+        <v>0.5740067335355765</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01309420256750498</v>
+        <v>0.03311361424304719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7842503451724476</v>
+        <v>0.7906892371785995</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01396590888389241</v>
+        <v>0.02523669772110575</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6848074942555608</v>
+        <v>0.6958643630462426</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05068447536484409</v>
+        <v>0.06463890173652391</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[106, 34], [7, 8]]</t>
+          <t>[[107, 34], [6, 9]]</t>
         </is>
       </c>
     </row>
